--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>아이디</t>
   </si>
@@ -65,6 +65,9 @@
     <t>계산 방식</t>
   </si>
   <si>
+    <t>스프라이트 주소</t>
+  </si>
+  <si>
     <t>설명</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
     <t>UpgradeValue</t>
   </si>
   <si>
+    <t>SpritePath</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -134,6 +140,9 @@
     <t>Sum</t>
   </si>
   <si>
+    <t>Upgrade/CargoExpand</t>
+  </si>
+  <si>
     <t>Expand Ship Storage</t>
   </si>
   <si>
@@ -143,6 +152,9 @@
     <t>Engine Overclock</t>
   </si>
   <si>
+    <t>Upgrade/EngineOverclock</t>
+  </si>
+  <si>
     <t>Improve Speed Limit</t>
   </si>
   <si>
@@ -155,6 +167,9 @@
     <t>Multi</t>
   </si>
   <si>
+    <t>Upgrade/EnhancedNozzle</t>
+  </si>
+  <si>
     <t>Add Nozzle to Accelate Much Faster</t>
   </si>
   <si>
@@ -164,6 +179,9 @@
     <t>Extra Fuel Tank</t>
   </si>
   <si>
+    <t>Upgrade/ExtraFuelTank</t>
+  </si>
+  <si>
     <t>Can Store More Fuel</t>
   </si>
   <si>
@@ -179,6 +197,9 @@
     <t>Nano Refiner</t>
   </si>
   <si>
+    <t>Upgrade/NanoRefiner</t>
+  </si>
+  <si>
     <t>Apply Nano Technology in Refiner</t>
   </si>
   <si>
@@ -186,6 +207,9 @@
   </si>
   <si>
     <t>Hydroponics</t>
+  </si>
+  <si>
+    <t>Upgrade/Hydroponics</t>
   </si>
   <si>
     <t>Upgrade Food ValueChain</t>
@@ -355,18 +379,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -693,7 +711,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,16 +735,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -735,96 +753,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1358,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1373,10 +1388,11 @@
     <col min="10" max="10" width="11.2222222222222" customWidth="1"/>
     <col min="11" max="11" width="14.4444444444444" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="32.2222222222222" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="32.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1416,101 +1432,110 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="M3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1527,31 +1552,34 @@
       <c r="I4">
         <v>5</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
       <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1568,31 +1596,34 @@
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>10</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>5</v>
       </c>
       <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>40</v>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1609,34 +1640,37 @@
       <c r="I6">
         <v>25</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>1</v>
       </c>
       <c r="K6">
         <v>1.2</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:13">
+    <row r="7" customFormat="1" spans="1:14">
       <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>44</v>
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>2000</v>
@@ -1657,24 +1691,27 @@
         <v>100</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="N7" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1698,27 +1735,30 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>50</v>
+        <v>56</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>1000</v>
@@ -1739,30 +1779,33 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M9" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="3"/>
+    <row r="10" spans="1:14">
+      <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:13">
-      <c r="B11" s="3"/>
+    <row r="11" spans="1:14">
+      <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+    <row r="12" spans="1:14">
+      <c r="B12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="3"/>
+    <row r="13" spans="1:14">
+      <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:13">
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="K14" s="4"/>
+    <row r="14" spans="1:14">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="14136" windowHeight="8111"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1553,7 +1553,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K4" s="3">
         <v>10</v>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -1773,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L9" t="s">
         <v>45</v>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14136" windowHeight="8111"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>아이디</t>
   </si>
@@ -56,6 +56,12 @@
     <t>주괴 증가</t>
   </si>
   <si>
+    <t>기본 광석 비용</t>
+  </si>
+  <si>
+    <t>광석 증가</t>
+  </si>
+  <si>
     <t>기본 스텟</t>
   </si>
   <si>
@@ -111,6 +117,12 @@
   </si>
   <si>
     <t>IngotIncrease</t>
+  </si>
+  <si>
+    <t>BaseOreCost</t>
+  </si>
+  <si>
+    <t>OreIncrease</t>
   </si>
   <si>
     <t>BaseStats</t>
@@ -1373,7 +1385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1381,18 +1393,18 @@
     <col min="3" max="3" width="13.7777777777778" customWidth="1"/>
     <col min="4" max="4" width="16.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="11.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.5555555555556" customWidth="1"/>
+    <col min="6" max="6" width="15.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="13.5555555555556" customWidth="1"/>
     <col min="8" max="8" width="14.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="13.8888888888889" customWidth="1"/>
-    <col min="10" max="10" width="11.2222222222222" customWidth="1"/>
-    <col min="11" max="11" width="14.4444444444444" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="32.2222222222222" customWidth="1"/>
+    <col min="9" max="11" width="13.8888888888889" customWidth="1"/>
+    <col min="12" max="12" width="11.2222222222222" customWidth="1"/>
+    <col min="13" max="13" width="14.4444444444444" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="32.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1435,107 +1447,125 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1552,34 +1582,40 @@
       <c r="I4">
         <v>5</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
         <v>20</v>
       </c>
-      <c r="K4" s="3">
+      <c r="M4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="N4" t="s">
+      <c r="C5" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1596,34 +1632,40 @@
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
         <v>10</v>
       </c>
-      <c r="K5" s="3">
+      <c r="M5" s="3">
         <v>5</v>
       </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1640,34 +1682,40 @@
       <c r="I6">
         <v>25</v>
       </c>
-      <c r="J6" s="3">
-        <v>1</v>
+      <c r="J6">
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1.2</v>
-      </c>
-      <c r="L6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" t="s">
-        <v>46</v>
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="O6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P6" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:14">
+    <row r="7" customFormat="1" spans="1:16">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1685,42 +1733,48 @@
         <v>10</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>200</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>100</v>
       </c>
-      <c r="L7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" t="s">
-        <v>50</v>
-      </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="O7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
         <v>2000</v>
-      </c>
-      <c r="G8">
-        <v>1000</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1729,83 +1783,95 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>50</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8">
         <v>5</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>5</v>
       </c>
-      <c r="L8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" t="s">
-        <v>56</v>
-      </c>
       <c r="N8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
+      <c r="C9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G9">
         <v>1000</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K9">
         <v>30</v>
       </c>
-      <c r="L9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" t="s">
-        <v>60</v>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>30</v>
       </c>
       <c r="N9" t="s">
-        <v>61</v>
+        <v>49</v>
+      </c>
+      <c r="O9" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:16">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:16">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:16">
       <c r="B12" s="2"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:16">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:16">
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="M14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>아이디</t>
   </si>
@@ -56,12 +56,6 @@
     <t>주괴 증가</t>
   </si>
   <si>
-    <t>기본 광석 비용</t>
-  </si>
-  <si>
-    <t>광석 증가</t>
-  </si>
-  <si>
     <t>기본 스텟</t>
   </si>
   <si>
@@ -117,12 +111,6 @@
   </si>
   <si>
     <t>IngotIncrease</t>
-  </si>
-  <si>
-    <t>BaseOreCost</t>
-  </si>
-  <si>
-    <t>OreIncrease</t>
   </si>
   <si>
     <t>BaseStats</t>
@@ -1385,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1396,15 +1384,15 @@
     <col min="6" max="6" width="15.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="13.5555555555556" customWidth="1"/>
     <col min="8" max="8" width="14.2222222222222" customWidth="1"/>
-    <col min="9" max="11" width="13.8888888888889" customWidth="1"/>
-    <col min="12" max="12" width="11.2222222222222" customWidth="1"/>
-    <col min="13" max="13" width="14.4444444444444" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="23" customWidth="1"/>
-    <col min="16" max="16" width="32.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="13.8888888888889" customWidth="1"/>
+    <col min="10" max="10" width="11.2222222222222" customWidth="1"/>
+    <col min="11" max="11" width="14.4444444444444" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="32.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1447,125 +1435,107 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
+      <c r="M3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="1" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="D4" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1582,40 +1552,34 @@
       <c r="I4">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
+      <c r="J4" s="3">
         <v>20</v>
       </c>
-      <c r="M4" s="3">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
       <c r="N4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
         <v>40</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1632,40 +1596,34 @@
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="J5" s="3">
         <v>10</v>
       </c>
-      <c r="M5" s="3">
+      <c r="K5" s="3">
         <v>5</v>
       </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
       <c r="N5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1682,40 +1640,34 @@
       <c r="I6">
         <v>25</v>
       </c>
-      <c r="J6">
-        <v>0</v>
+      <c r="J6" s="3">
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>2</v>
-      </c>
-      <c r="M6">
         <v>30</v>
       </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
       <c r="N6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:14">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="O6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:16">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1733,39 +1685,33 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>200</v>
-      </c>
-      <c r="M7">
         <v>100</v>
       </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s">
+        <v>50</v>
+      </c>
       <c r="N7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P7" t="s">
+      <c r="D8" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1783,39 +1729,33 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>50</v>
-      </c>
-      <c r="L8">
         <v>5</v>
       </c>
-      <c r="M8">
-        <v>5</v>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s">
+        <v>56</v>
       </c>
       <c r="N8" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -1827,51 +1767,45 @@
         <v>1000</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <v>30</v>
       </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>30</v>
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" t="s">
+        <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>49</v>
-      </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:14">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:14">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:14">
       <c r="B12" s="2"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:14">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:14">
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="16524" windowHeight="7800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>아이디</t>
   </si>
@@ -143,7 +143,7 @@
     <t>Upgrade/CargoExpand</t>
   </si>
   <si>
-    <t>Expand Ship Storage</t>
+    <t>Modular cargo bay expansion using advanced polymer alloy frames</t>
   </si>
   <si>
     <t>UP_Ship_Speed</t>
@@ -155,7 +155,7 @@
     <t>Upgrade/EngineOverclock</t>
   </si>
   <si>
-    <t>Improve Speed Limit</t>
+    <t>Overclock engine output beyond factory limits for higher top speed</t>
   </si>
   <si>
     <t>UP_Ship_Accel</t>
@@ -170,7 +170,7 @@
     <t>Upgrade/EnhancedNozzle</t>
   </si>
   <si>
-    <t>Add Nozzle to Accelate Much Faster</t>
+    <t>Retrofitted plasma nozzle array delivers explosive burst acceleration</t>
   </si>
   <si>
     <t>UP_Ship_MaxFuel</t>
@@ -182,7 +182,7 @@
     <t>Upgrade/ExtraFuelTank</t>
   </si>
   <si>
-    <t>Can Store More Fuel</t>
+    <t>High-pressure void fuel cells extend operational range significantly</t>
   </si>
   <si>
     <t>UP_Stat_Refine</t>
@@ -200,7 +200,7 @@
     <t>Upgrade/NanoRefiner</t>
   </si>
   <si>
-    <t>Apply Nano Technology in Refiner</t>
+    <t>Nanoscale refinery bots process raw ore with unprecedented efficiency</t>
   </si>
   <si>
     <t>UP_Stat_Farm</t>
@@ -212,7 +212,43 @@
     <t>Upgrade/Hydroponics</t>
   </si>
   <si>
-    <t>Upgrade Food ValueChain</t>
+    <t>Zero-gravity hydroponic systems maximize food production yield</t>
+  </si>
+  <si>
+    <t>UP_Ship_FuelRegen</t>
+  </si>
+  <si>
+    <t>VoidCrystalResonator</t>
+  </si>
+  <si>
+    <t>Upgrade/VoidCrystalResonator</t>
+  </si>
+  <si>
+    <t>Harness crystallized void energy to accelerate fuel regeneration</t>
+  </si>
+  <si>
+    <t>UP_Ship_DockingSpeed</t>
+  </si>
+  <si>
+    <t>MagneticDockingSystem</t>
+  </si>
+  <si>
+    <t>Upgrade/MagneticDockingSystem</t>
+  </si>
+  <si>
+    <t>Electromagnetic lock system pulls your ship into dock at high speed</t>
+  </si>
+  <si>
+    <t>UP_Ship_LoaderSpeed</t>
+  </si>
+  <si>
+    <t>GravitonCargoManipulator</t>
+  </si>
+  <si>
+    <t>Upgrade/GravitonCargoManipulator</t>
+  </si>
+  <si>
+    <t>Graviton field technology dramatically speeds up cargo loading and unloading</t>
   </si>
 </sst>
 </file>
@@ -835,14 +871,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1376,20 +1418,19 @@
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="22.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="12.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="13.7777777777778" customWidth="1"/>
-    <col min="4" max="4" width="16.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="24.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="11.3333333333333" customWidth="1"/>
     <col min="6" max="6" width="15.2222222222222" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" customWidth="1"/>
-    <col min="8" max="8" width="14.2222222222222" customWidth="1"/>
+    <col min="7" max="8" width="13.5555555555556" customWidth="1"/>
     <col min="9" max="9" width="13.8888888888889" customWidth="1"/>
     <col min="10" max="10" width="11.2222222222222" customWidth="1"/>
     <col min="11" max="11" width="14.4444444444444" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="32.2222222222222" customWidth="1"/>
+    <col min="13" max="13" width="33.9814814814815" customWidth="1"/>
+    <col min="14" max="14" width="67.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1493,7 +1534,7 @@
       <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1531,13 +1572,13 @@
       <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>10</v>
       </c>
       <c r="F4">
@@ -1552,10 +1593,10 @@
       <c r="I4">
         <v>5</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="5">
         <v>20</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
       <c r="L4" t="s">
@@ -1575,13 +1616,13 @@
       <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>5</v>
       </c>
       <c r="F5">
@@ -1596,10 +1637,10 @@
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="5">
         <v>10</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="5">
         <v>5</v>
       </c>
       <c r="L5" t="s">
@@ -1619,13 +1660,13 @@
       <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>5</v>
       </c>
       <c r="F6">
@@ -1640,7 +1681,7 @@
       <c r="I6">
         <v>25</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="5">
         <v>2</v>
       </c>
       <c r="K6">
@@ -1660,16 +1701,16 @@
       <c r="A7" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>10</v>
       </c>
       <c r="F7">
@@ -1707,13 +1748,13 @@
       <c r="B8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>55</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>5</v>
       </c>
       <c r="F8">
@@ -1751,13 +1792,13 @@
       <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>10</v>
       </c>
       <c r="F9">
@@ -1789,23 +1830,144 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="B10" s="2"/>
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="4">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>2000</v>
+      </c>
+      <c r="G10">
+        <v>2000</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="B11" s="2"/>
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="4">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>20</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="B12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="4">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>25</v>
+      </c>
+      <c r="J12">
+        <v>0.1</v>
+      </c>
+      <c r="K12">
+        <v>-0.005</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" t="s">
+        <v>72</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="B13" s="2"/>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="K14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16524" windowHeight="7800"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1770,13 +1770,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M8" t="s">
         <v>56</v>
@@ -1802,10 +1802,10 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1817,7 +1817,7 @@
         <v>2</v>
       </c>
       <c r="K9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L9" t="s">
         <v>45</v>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -1588,16 +1588,16 @@
         <v>500</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K4" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
@@ -1632,10 +1632,10 @@
         <v>300</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>10</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J6" s="5">
         <v>2</v>
@@ -1720,10 +1720,10 @@
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>200</v>
@@ -1758,10 +1758,10 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G8">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1808,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -1896,10 +1896,10 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1940,16 +1940,16 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J12">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="K12">
-        <v>-0.005</v>
+        <v>-0.0025</v>
       </c>
       <c r="L12" t="s">
         <v>36</v>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -1638,7 +1638,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>5</v>
@@ -1685,7 +1685,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
         <v>45</v>
@@ -1773,7 +1773,7 @@
         <v>2</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L8" t="s">
         <v>45</v>
@@ -1817,7 +1817,7 @@
         <v>2</v>
       </c>
       <c r="K9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L9" t="s">
         <v>45</v>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1641,7 +1641,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" t="s">
         <v>36</v>
@@ -1729,7 +1729,7 @@
         <v>200</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G4">
         <v>500</v>
@@ -1629,7 +1629,7 @@
         <v>500</v>
       </c>
       <c r="G5">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G6">
         <v>1000</v>
@@ -1714,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -1846,10 +1846,10 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G10">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>15</v>
       </c>
       <c r="I12">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>0.05</v>
